--- a/010.Cut Copy Paste.xlsx
+++ b/010.Cut Copy Paste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB0513B-0F5B-43FE-A2FE-5B8ACEEB5B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17126E8-8144-47E1-B573-7CD1935F931C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4230" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,22 +511,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:P16"/>
+  <dimension ref="B3:P16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
     <col min="11" max="11" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,7 +555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>5</v>
       </c>
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>6</v>
       </c>
@@ -603,7 +603,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -643,7 +643,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>10</v>
       </c>
@@ -683,7 +683,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>12</v>
       </c>
@@ -723,7 +723,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K10" t="s">
         <v>14</v>
       </c>
@@ -744,7 +744,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -753,12 +753,12 @@
         <v>740</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>15</v>
       </c>
@@ -767,12 +767,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -781,7 +781,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K16" t="s">
         <v>16</v>
       </c>

--- a/010.Cut Copy Paste.xlsx
+++ b/010.Cut Copy Paste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17126E8-8144-47E1-B573-7CD1935F931C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D60C618-9C81-40CC-91CE-B22AB0954BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4230" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,22 +511,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:P16"/>
+  <dimension ref="B3:G31"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
     <col min="11" max="11" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,31 +536,13 @@
       <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="K5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>6</v>
       </c>
@@ -583,27 +562,8 @@
         <f>SUM(C6:F6)</f>
         <v>560</v>
       </c>
-      <c r="K6" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>250</v>
-      </c>
-      <c r="M6">
-        <v>385</v>
-      </c>
-      <c r="N6">
-        <v>755</v>
-      </c>
-      <c r="O6">
-        <v>550</v>
-      </c>
-      <c r="P6">
-        <f>SUM(L6:O6)</f>
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -623,27 +583,8 @@
         <f>SUM(C7:F7)</f>
         <v>855</v>
       </c>
-      <c r="K7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>380</v>
-      </c>
-      <c r="M7">
-        <v>410</v>
-      </c>
-      <c r="N7">
-        <v>230</v>
-      </c>
-      <c r="O7">
-        <v>475</v>
-      </c>
-      <c r="P7">
-        <f>SUM(L7:O7)</f>
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>10</v>
       </c>
@@ -663,27 +604,8 @@
         <f>SUM(C8:F8)</f>
         <v>900</v>
       </c>
-      <c r="K8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L8">
-        <v>110</v>
-      </c>
-      <c r="M8">
-        <v>170</v>
-      </c>
-      <c r="N8">
-        <v>325</v>
-      </c>
-      <c r="O8">
-        <v>350</v>
-      </c>
-      <c r="P8">
-        <f>SUM(L8:O8)</f>
-        <v>955</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>12</v>
       </c>
@@ -703,48 +625,8 @@
         <f>SUM(C9:F9)</f>
         <v>850</v>
       </c>
-      <c r="K9" t="s">
-        <v>13</v>
-      </c>
-      <c r="L9">
-        <v>460</v>
-      </c>
-      <c r="M9">
-        <v>525</v>
-      </c>
-      <c r="N9">
-        <v>580</v>
-      </c>
-      <c r="O9">
-        <v>685</v>
-      </c>
-      <c r="P9">
-        <f>SUM(L9:O9)</f>
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="K10" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10">
-        <v>500</v>
-      </c>
-      <c r="M10">
-        <v>335</v>
-      </c>
-      <c r="N10">
-        <v>450</v>
-      </c>
-      <c r="O10">
-        <v>610</v>
-      </c>
-      <c r="P10">
-        <f>SUM(L10:O10)</f>
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -753,12 +635,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="K12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>15</v>
       </c>
@@ -767,12 +644,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="K14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -781,8 +653,150 @@
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="K16" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>250</v>
+      </c>
+      <c r="D21">
+        <v>385</v>
+      </c>
+      <c r="E21">
+        <v>755</v>
+      </c>
+      <c r="F21">
+        <v>550</v>
+      </c>
+      <c r="G21">
+        <f>SUM(C21:F21)</f>
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>380</v>
+      </c>
+      <c r="D22">
+        <v>410</v>
+      </c>
+      <c r="E22">
+        <v>230</v>
+      </c>
+      <c r="F22">
+        <v>475</v>
+      </c>
+      <c r="G22">
+        <f>SUM(C22:F22)</f>
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23">
+        <v>110</v>
+      </c>
+      <c r="D23">
+        <v>170</v>
+      </c>
+      <c r="E23">
+        <v>325</v>
+      </c>
+      <c r="F23">
+        <v>350</v>
+      </c>
+      <c r="G23">
+        <f>SUM(C23:F23)</f>
+        <v>955</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24">
+        <v>460</v>
+      </c>
+      <c r="D24">
+        <v>525</v>
+      </c>
+      <c r="E24">
+        <v>580</v>
+      </c>
+      <c r="F24">
+        <v>685</v>
+      </c>
+      <c r="G24">
+        <f>SUM(C24:F24)</f>
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>500</v>
+      </c>
+      <c r="D25">
+        <v>335</v>
+      </c>
+      <c r="E25">
+        <v>450</v>
+      </c>
+      <c r="F25">
+        <v>610</v>
+      </c>
+      <c r="G25">
+        <f>SUM(C25:F25)</f>
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
         <v>16</v>
       </c>
     </row>
